--- a/ipl_report.xlsx
+++ b/ipl_report.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,17 +421,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Batsman</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Runs</t>
         </is>
@@ -724,17 +712,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Bowler</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Wickets</t>
         </is>
@@ -1015,17 +1003,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Wins</t>
         </is>
@@ -1041,7 +1029,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
@@ -1067,7 +1055,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5">
@@ -1080,7 +1068,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6">
@@ -1093,7 +1081,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7">
@@ -1106,7 +1094,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -1119,7 +1107,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -1132,7 +1120,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1241,17 +1229,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total Runs</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Matches Played</t>
         </is>
@@ -1277,10 +1265,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16020</v>
+        <v>16353</v>
       </c>
       <c r="C3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -1290,10 +1278,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18592</v>
+        <v>18883</v>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1329,10 +1317,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21977</v>
+        <v>22602</v>
       </c>
       <c r="C7" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -1342,10 +1330,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18605</v>
+        <v>18931</v>
       </c>
       <c r="C8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -1355,10 +1343,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17561</v>
+        <v>17964</v>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -1381,10 +1369,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18463</v>
+        <v>18786</v>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -1407,10 +1395,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18603</v>
+        <v>19331</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -1420,10 +1408,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17958</v>
+        <v>19416</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -1433,10 +1421,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18304</v>
+        <v>18637</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
@@ -1493,22 +1481,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Toss Decision</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Won After Toss</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Win %</t>
         </is>
@@ -1521,13 +1509,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C2" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D2" t="n">
-        <v>45.31</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="3">
@@ -1537,13 +1525,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="C3" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D3" t="n">
-        <v>54.05</v>
+        <v>53.86</v>
       </c>
     </row>
   </sheetData>
